--- a/Configs/Datas/#ZZZ.Buff.xlsx
+++ b/Configs/Datas/#ZZZ.Buff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1FCD3F-128F-472E-8C07-B5C797DFD6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41303ABE-4A64-4556-8424-9F58B3B2D820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -178,6 +178,14 @@
   </si>
   <si>
     <t>PerfectEvade,None,None,0,0.1,5,true,""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性加成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyAttribute,None,Resilience,0,5,0,false,""</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -542,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="10.875" customWidth="1"/>
@@ -734,6 +742,32 @@
         <v>39</v>
       </c>
     </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>9002</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7">
+        <v>-1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
